--- a/paper/supplementary_data/Supplementary_Data_4_teacher_manifests.xlsx
+++ b/paper/supplementary_data/Supplementary_Data_4_teacher_manifests.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="response_priors" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="teacher_sources" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="endpoint_sources" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="response priors" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="teacher sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="endpoint sources" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="identity audit" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,14 +432,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="57" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,12 +450,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>prior_name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>physical_meaning</t>
+          <t>physical meaning</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -464,17 +465,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>target_units</t>
+          <t>units</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_class</t>
+          <t>surrogate</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>training_size</t>
+          <t>training rows</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -484,7 +485,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>inference_computation</t>
+          <t>inference</t>
         </is>
       </c>
     </row>
@@ -494,17 +495,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>combisolv_qm_teacher</t>
+          <t>combisolv_qm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COSMOtherm hydration response</t>
+          <t>COSMOtherm water response</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CombiSolv-QM water</t>
+          <t>CombiSolv-QM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,20 +515,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CHEMELEON-initialized D-MPNN</t>
+          <t>CHEMELEON D-MPNN</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3963</v>
+        <v>3959</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -537,17 +538,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abraham_e_teacher</t>
+          <t>abraham_e</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>excess molar refraction axis E</t>
+          <t>excess molar refraction E</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SoluteML Abraham</t>
+          <t>SoluteML</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -565,12 +566,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -580,17 +581,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abraham_s_teacher</t>
+          <t>abraham_s</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dipolarity/polarizability axis S</t>
+          <t>dipolarity/polarizability S</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SoluteML Abraham</t>
+          <t>SoluteML</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,12 +609,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -623,17 +624,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>abraham_a_teacher</t>
+          <t>abraham_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hydrogen-bond acidity axis A</t>
+          <t>hydrogen-bond acidity A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SoluteML Abraham</t>
+          <t>SoluteML</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -651,12 +652,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -666,17 +667,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>abraham_b_teacher</t>
+          <t>abraham_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hydrogen-bond basicity axis B</t>
+          <t>hydrogen-bond basicity B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SoluteML Abraham</t>
+          <t>SoluteML</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -694,12 +695,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -709,17 +710,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>abraham_l_teacher</t>
+          <t>abraham_l</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hexadecane-air partition axis L</t>
+          <t>hexadecane-air partition L</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SoluteML Abraham</t>
+          <t>SoluteML</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -737,12 +738,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -752,12 +753,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>openff_corrected_teacher</t>
+          <t>openff_corrected</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>explicit-water alchemical hydration response</t>
+          <t>explicit-water alchemical response</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -780,12 +781,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>predicted calculation + predicted experimental residual</t>
+          <t>prediction + residual</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -795,7 +796,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gbn2_corrected_teacher</t>
+          <t>gbn2_corrected</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -805,7 +806,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GBn2 / GNNImplicitSolvent</t>
+          <t>GBn2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -823,12 +824,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>predicted GBn2 value + predicted experimental residual</t>
+          <t>prediction + residual</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -838,12 +839,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>molsolv_smd_teacher</t>
+          <t>smd_water</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SMD(water) solvation response</t>
+          <t>SMD water response</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -858,20 +859,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CHEMELEON-initialized D-MPNN</t>
+          <t>CHEMELEON D-MPNN</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>350391</v>
+        <v>350359</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -881,12 +882,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>confsolv_gas_conformer_correction_teacher</t>
+          <t>conf_gas_corr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gas conformer free-energy correction</t>
+          <t>gas conformer correction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -905,16 +906,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>39878</v>
+        <v>17829</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -924,12 +925,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>confsolv_solution_conformer_correction_teacher</t>
+          <t>conf_solution_corr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>solution conformer free-energy correction</t>
+          <t>solution conformer correction</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -948,16 +949,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>39878</v>
+        <v>17829</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -967,7 +968,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>confsolv_hydration_conformer_correction_teacher</t>
+          <t>conf_hydration_corr</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -991,16 +992,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>39878</v>
+        <v>17829</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1011,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>confsolv_water_gsolv_std_teacher</t>
+          <t>conf_gsolv_sd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dispersion of conformer solvation energies</t>
+          <t>conformer solvation-energy spread</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1034,16 +1035,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>39878</v>
+        <v>17829</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1054,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>confsolv_water_response_mean_teacher</t>
+          <t>conf_response_mean</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1077,16 +1078,16 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>39878</v>
+        <v>17829</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1097,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>confsolv_water_response_std_teacher</t>
+          <t>conf_response_sd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dispersion of conformer solvent response</t>
+          <t>conformer response spread</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1120,16 +1121,16 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>39878</v>
+        <v>17829</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>direct surrogate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>structure-derived surrogate prediction; no simulation</t>
+          <t>structure surrogate; no simulation</t>
         </is>
       </c>
     </row>
@@ -1144,23 +1145,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="59" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1171,437 +1164,131 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>scientific_role</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>processed_file</t>
+          <t>before standardized exclusion</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>original_records</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>filtered_records</t>
+          <t>retained</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>benchmark_overlaps_removed</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>doi</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>license</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>redistributed</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>reproduction_command</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>processed_bytes</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>processed_sha256</t>
+          <t>role</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MolSolv SMD(water)</t>
+          <t>CombiSolv-QM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>water-specific quantum-continuum response teacher</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>molsolv_smd_water_nonbenchmark.parquet</t>
-        </is>
+          <t>unique structures</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3961</v>
       </c>
       <c r="D2" t="n">
-        <v>1729545</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>350391</v>
-      </c>
-      <c r="F2" t="n">
-        <v>82</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Zenodo record 7262826</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/records/7262826</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10.5281/zenodo.7262826</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>python scripts/download_data.py molsolv</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>17353622</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>758b9b56a991d874fb1067eca024dbc2244e67f8c8eb319db08ec4ab33e07460</t>
+        <v>3959</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>COSMOtherm water</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ConfSolv H2O</t>
+          <t>MolSolv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>water conformer and solvent-response hierarchy</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>confsolv_water_nonbenchmark.parquet</t>
-        </is>
+          <t>SMD calculations</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>350391</v>
       </c>
       <c r="D3" t="n">
-        <v>5392567</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>39878</v>
-      </c>
-      <c r="F3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Zenodo record 8292520</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/records/8292520</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10.5281/zenodo.8292520</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>python scripts/download_data.py confsolv</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>10233975</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>d283d2da04987a1802dbf60c5606394ac745c26609e2628144874b27bd037e27</t>
+        <v>350359</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SMD(water)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SoluteML Abraham</t>
+          <t>ConfSolv</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>empirical solute-response axes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>soluteml_abraham_nonbenchmark.parquet</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>model-usable connectivities</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>17851</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22</v>
+      </c>
       <c r="E4" t="n">
-        <v>8098</v>
-      </c>
-      <c r="F4" t="n">
-        <v>84</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Zenodo record 5792296</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/records/5792296</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10.1021/acs.jcim.1c01103</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>python scripts/download_data.py soluteml</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>632777</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4b90805c619a53b3b25a479c5c6b393333b575473738d5b290d899fb4a3e5fa2</t>
+        <v>17829</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>conformer response</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpenFE/OpenFF 2.3.0 FreeSolv ASFE</t>
+          <t>Endpoint labels</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>explicit-water alchemical response teacher</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>openff_alchemical_nonbenchmark.parquet</t>
-        </is>
+          <t>experimental connectivities</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1280</v>
       </c>
       <c r="D5" t="n">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>520</v>
-      </c>
-      <c r="F5" t="n">
-        <v>83</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Zenodo record 21810272</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/records/21810272</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10.5281/zenodo.21810272</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>python scripts/download_data.py openff</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>82697</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3d34e27040d69fe01c45b0b9e6424baee2ba9e3c220bc6659a89d30232f9b087</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GBn2 / GNNImplicitSolvent</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>implicit and learned explicit-water response teacher</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>implicit_solvent_nonbenchmark.parquet</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>550</v>
-      </c>
-      <c r="E6" t="n">
-        <v>550</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>repository state recorded in global catalog</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://github.com/rinikerlab/GNNImplicitSolvent</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10.1039/D4SC02432J</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>CC-BY-SA-4.0 data</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>python scripts/download_data.py implicit</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>59940</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1a50219f3a0c0c60a754b430b4bc9c6c26beea1ed198e76e8aef7b14a8fa13a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CombiSolv-QM water</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>COSMOtherm water-response teacher</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>combisolv_qm_water_nonbenchmark.parquet</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3988</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3963</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Chemical Engineering Journal supplementary file</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://ars.els-cdn.com/content/image/1-s2.0-S1385894721008925-mmc1.txt</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10.1016/j.cej.2021.129307</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>publisher supplementary terms; no standalone data license</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>python scripts/download_data.py combisolv-qm --accept-source-terms</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>283353</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>6fbaceff441b62c8399aae2dbd3b6cfbdfa10b86fc47cee8d60001c73da24832</t>
+        <v>1280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hydration free energy</t>
         </is>
       </c>
     </row>
@@ -1616,34 +1303,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>source_group</t>
+          <t>source group</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>selected_records</t>
+          <t>selected records</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>selection_rule</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>endpoint_target</t>
+          <t>selection rule</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1339,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>legacy benchmark-disjoint merge</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>experimental hydration</t>
+          <t>benchmark-disjoint connectivity</t>
         </is>
       </c>
     </row>
@@ -1678,19 +1354,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>legacy benchmark-disjoint merge</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>experimental solvation in water</t>
+          <t>water records; benchmark-disjoint connectivity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FreeSolv + CombiSolv-Exp identity</t>
+          <t>FreeSolv + CombiSolv-Exp</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1698,12 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>one connectivity-level merged record</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>duplicate-resolved experimental hydration</t>
+          <t>one duplicate-resolved connectivity</t>
         </is>
       </c>
     </row>
@@ -1721,10 +1387,375 @@
           <t>at least two source measurements</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>consensus experimental hydration</t>
-        </is>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source_rows</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>unique_smiles_audited</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>parse_failures</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>full_inchi_key_matches</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>connectivity_matches</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fragment_parent_matches</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>uncharged_parent_matches</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>canonical_tautomer_matches</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_sharing_benchmark_scaffold</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>maximum_similarity</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>median_of_benchmark_max_similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>endpoint_experimental</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>439</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>combisolv_qm</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3963</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3963</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>874</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>abraham</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8098</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8098</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>openff</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>520</v>
+      </c>
+      <c r="C5" t="n">
+        <v>520</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>190</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gbn2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>550</v>
+      </c>
+      <c r="C6" t="n">
+        <v>550</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>206</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>molsolv_smd</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>350391</v>
+      </c>
+      <c r="C7" t="n">
+        <v>350391</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>32</v>
+      </c>
+      <c r="J7" t="n">
+        <v>51943</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>confsolv</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>39878</v>
+      </c>
+      <c r="C8" t="n">
+        <v>39878</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22</v>
+      </c>
+      <c r="I8" t="n">
+        <v>22</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7008</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
